--- a/data/trans_orig/P6704-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6704-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le cuesta olvidar los problemas del trabajo en 2012</t>
+          <t>Población según si le cuesta olvidar los problemas del trabajo en 2012 (tasa de respuesta: 99,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47899</t>
+          <t>45927</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74555</t>
+          <t>75422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22497</t>
+          <t>22575</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43934</t>
+          <t>42988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75622</t>
+          <t>75193</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111304</t>
+          <t>110624</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43544</t>
+          <t>44095</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70310</t>
+          <t>72490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28162</t>
+          <t>28434</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50014</t>
+          <t>52380</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78567</t>
+          <t>78378</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114184</t>
+          <t>112548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66458</t>
+          <t>66346</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>97013</t>
+          <t>95558</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39235</t>
+          <t>39595</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62671</t>
+          <t>64202</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112578</t>
+          <t>112726</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>151316</t>
+          <t>151934</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29703</t>
+          <t>30462</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52675</t>
+          <t>53867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15222</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34437</t>
+          <t>34140</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50306</t>
+          <t>49941</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80104</t>
+          <t>80809</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>21251</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41813</t>
+          <t>42795</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>9394</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24852</t>
+          <t>24153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35234</t>
+          <t>34477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63318</t>
+          <t>60981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85944</t>
+          <t>86730</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53201</t>
+          <t>53150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83050</t>
+          <t>83930</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116086</t>
+          <t>113072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159247</t>
+          <t>157481</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60089</t>
+          <t>60520</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93491</t>
+          <t>94829</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30336</t>
+          <t>31652</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54881</t>
+          <t>55188</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99861</t>
+          <t>100523</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>142054</t>
+          <t>140739</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>108427</t>
+          <t>108276</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>147443</t>
+          <t>146702</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59424</t>
+          <t>59879</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89118</t>
+          <t>90237</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>178951</t>
+          <t>176442</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>225978</t>
+          <t>223920</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49178</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78380</t>
+          <t>79483</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30331</t>
+          <t>31605</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55414</t>
+          <t>55452</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88010</t>
+          <t>87499</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126027</t>
+          <t>126576</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60259</t>
+          <t>59780</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92198</t>
+          <t>93157</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31646</t>
+          <t>31268</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56595</t>
+          <t>57659</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97953</t>
+          <t>97218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>139371</t>
+          <t>139352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56583</t>
+          <t>56699</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89222</t>
+          <t>87858</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28507</t>
+          <t>29207</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53611</t>
+          <t>53075</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90150</t>
+          <t>91734</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133753</t>
+          <t>131265</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>35846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65211</t>
+          <t>63531</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28208</t>
+          <t>28925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52049</t>
+          <t>54130</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70673</t>
+          <t>69903</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108889</t>
+          <t>110141</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71398</t>
+          <t>72062</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>104167</t>
+          <t>103733</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41552</t>
+          <t>41125</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69550</t>
+          <t>69001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>121539</t>
+          <t>123547</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>166188</t>
+          <t>165130</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>29569</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53430</t>
+          <t>51905</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18238</t>
+          <t>17405</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38201</t>
+          <t>37556</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52100</t>
+          <t>50799</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84298</t>
+          <t>82324</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59480</t>
+          <t>58664</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91131</t>
+          <t>89587</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40706</t>
+          <t>38169</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67131</t>
+          <t>66568</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105895</t>
+          <t>104488</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146750</t>
+          <t>145989</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49575</t>
+          <t>50479</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82314</t>
+          <t>81299</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67397</t>
+          <t>67492</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99393</t>
+          <t>99990</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125722</t>
+          <t>126007</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>171482</t>
+          <t>167387</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61588</t>
+          <t>59490</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>95999</t>
+          <t>94494</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32181</t>
+          <t>31911</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>57804</t>
+          <t>55952</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>97503</t>
+          <t>99640</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>139912</t>
+          <t>139398</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>127174</t>
+          <t>127539</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>167866</t>
+          <t>166890</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>77971</t>
+          <t>78875</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>109270</t>
+          <t>110326</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>217250</t>
+          <t>215372</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>266831</t>
+          <t>267256</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68850</t>
+          <t>68514</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101173</t>
+          <t>103994</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44901</t>
+          <t>46091</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72764</t>
+          <t>74984</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>122383</t>
+          <t>124005</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>167623</t>
+          <t>168426</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32828</t>
+          <t>32999</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59096</t>
+          <t>60232</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34962</t>
+          <t>33654</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>52528</t>
+          <t>53617</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>86597</t>
+          <t>84959</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>234427</t>
+          <t>236036</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>294751</t>
+          <t>293962</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>193782</t>
+          <t>196643</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>250344</t>
+          <t>249781</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>445684</t>
+          <t>445592</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>529929</t>
+          <t>526806</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>232168</t>
+          <t>230590</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>291985</t>
+          <t>289447</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>139529</t>
+          <t>140304</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>186320</t>
+          <t>189136</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>382679</t>
+          <t>384908</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>462121</t>
+          <t>462701</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>411172</t>
+          <t>405344</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>479439</t>
+          <t>478961</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>243053</t>
+          <t>245619</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>302666</t>
+          <t>303592</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>668756</t>
+          <t>666891</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>758072</t>
+          <t>763008</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>201015</t>
+          <t>201926</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>256389</t>
+          <t>259664</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>131272</t>
+          <t>128809</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>178034</t>
+          <t>175371</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>345174</t>
+          <t>343976</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>417252</t>
+          <t>415858</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>195357</t>
+          <t>194708</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>253041</t>
+          <t>253580</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>110093</t>
+          <t>111563</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>157913</t>
+          <t>154979</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>321180</t>
+          <t>318245</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>390797</t>
+          <t>395965</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le cuesta olvidar los problemas del trabajo en 2016</t>
+          <t>Población según si le cuesta olvidar los problemas del trabajo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34115</t>
+          <t>34229</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58337</t>
+          <t>58716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32645</t>
+          <t>33359</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54263</t>
+          <t>55743</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73296</t>
+          <t>72699</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107400</t>
+          <t>106111</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29725</t>
+          <t>29165</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53448</t>
+          <t>53900</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28039</t>
+          <t>27733</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48653</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63456</t>
+          <t>63469</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96353</t>
+          <t>95408</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58045</t>
+          <t>58071</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87683</t>
+          <t>87252</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30136</t>
+          <t>31283</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52750</t>
+          <t>53727</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>94395</t>
+          <t>95577</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>133235</t>
+          <t>131483</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46624</t>
+          <t>46817</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74848</t>
+          <t>74612</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22468</t>
+          <t>21886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43035</t>
+          <t>43241</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76313</t>
+          <t>75632</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111243</t>
+          <t>110711</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16392</t>
+          <t>17443</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37388</t>
+          <t>37526</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21873</t>
+          <t>21788</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28507</t>
+          <t>28027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52455</t>
+          <t>52524</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86919</t>
+          <t>86975</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125237</t>
+          <t>124127</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62902</t>
+          <t>62840</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93064</t>
+          <t>92300</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161206</t>
+          <t>159804</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>206063</t>
+          <t>204479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50925</t>
+          <t>51298</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79711</t>
+          <t>81044</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37670</t>
+          <t>38569</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63116</t>
+          <t>64168</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>96961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137417</t>
+          <t>137442</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95619</t>
+          <t>92963</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>132869</t>
+          <t>131701</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58038</t>
+          <t>58779</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86126</t>
+          <t>87191</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>163545</t>
+          <t>162820</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>209022</t>
+          <t>210313</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67791</t>
+          <t>67528</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103007</t>
+          <t>101956</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41679</t>
+          <t>41173</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66546</t>
+          <t>67895</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115952</t>
+          <t>114537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158406</t>
+          <t>156341</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32427</t>
+          <t>34291</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59636</t>
+          <t>60724</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14386</t>
+          <t>13853</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31994</t>
+          <t>31928</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>52599</t>
+          <t>53716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>84689</t>
+          <t>84324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60860</t>
+          <t>62433</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94816</t>
+          <t>94925</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33149</t>
+          <t>32625</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56807</t>
+          <t>55695</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99643</t>
+          <t>98397</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140133</t>
+          <t>140223</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44393</t>
+          <t>44766</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74051</t>
+          <t>73118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50424</t>
+          <t>51026</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76814</t>
+          <t>78267</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>101277</t>
+          <t>103278</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>141966</t>
+          <t>143917</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>113137</t>
+          <t>112921</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>150259</t>
+          <t>151764</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78855</t>
+          <t>77547</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>111394</t>
+          <t>109137</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>203352</t>
+          <t>203691</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>251887</t>
+          <t>252297</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38669</t>
+          <t>37300</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66520</t>
+          <t>63702</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34157</t>
+          <t>33770</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58894</t>
+          <t>59816</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75658</t>
+          <t>77222</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113092</t>
+          <t>114126</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34068</t>
+          <t>34152</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60580</t>
+          <t>59688</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17127</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35643</t>
+          <t>35805</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55139</t>
+          <t>55836</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88857</t>
+          <t>88203</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85765</t>
+          <t>87171</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>120772</t>
+          <t>122060</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>82177</t>
+          <t>81235</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>114165</t>
+          <t>115100</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>178769</t>
+          <t>176290</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>226862</t>
+          <t>223912</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>65240</t>
+          <t>64638</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>97510</t>
+          <t>95480</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32829</t>
+          <t>32412</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>58668</t>
+          <t>57437</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>104276</t>
+          <t>104914</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>147371</t>
+          <t>146982</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>91528</t>
+          <t>91817</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>128065</t>
+          <t>127717</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>77371</t>
+          <t>78584</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>109647</t>
+          <t>110701</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>178571</t>
+          <t>180226</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>225747</t>
+          <t>227844</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53088</t>
+          <t>52580</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>81311</t>
+          <t>81207</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40205</t>
+          <t>39616</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65835</t>
+          <t>67048</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>98980</t>
+          <t>97823</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>137076</t>
+          <t>139246</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31752</t>
+          <t>31889</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>57101</t>
+          <t>58760</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>27817</t>
+          <t>27721</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50837</t>
+          <t>50997</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>64611</t>
+          <t>65834</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>100754</t>
+          <t>99489</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>297433</t>
+          <t>297852</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>365438</t>
+          <t>364025</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>232813</t>
+          <t>234818</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>288975</t>
+          <t>289169</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>547174</t>
+          <t>545117</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>635808</t>
+          <t>633923</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>217490</t>
+          <t>213395</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>273756</t>
+          <t>272993</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>171134</t>
+          <t>169954</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>219909</t>
+          <t>221574</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>403872</t>
+          <t>401456</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>478330</t>
+          <t>481446</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>392041</t>
+          <t>391655</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>462704</t>
+          <t>461577</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>271589</t>
+          <t>272475</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>330620</t>
+          <t>328926</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>679146</t>
+          <t>683088</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>772889</t>
+          <t>778465</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>231049</t>
+          <t>230783</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>288855</t>
+          <t>290176</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>156969</t>
+          <t>157072</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>205810</t>
+          <t>205160</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>403128</t>
+          <t>403486</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>482600</t>
+          <t>479824</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>137717</t>
+          <t>138043</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>186503</t>
+          <t>185178</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>80562</t>
+          <t>82201</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>119711</t>
+          <t>118316</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>229517</t>
+          <t>230405</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>291521</t>
+          <t>294417</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le cuesta olvidar los problemas del trabajo en 2023</t>
+          <t>Población según si le cuesta olvidar los problemas del trabajo en 2023 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15346</t>
+          <t>15771</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41299</t>
+          <t>40134</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20029</t>
+          <t>20954</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34715</t>
+          <t>35164</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41021</t>
+          <t>41234</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68575</t>
+          <t>69846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>44,36%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21412</t>
+          <t>21568</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10374</t>
+          <t>11172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>11854</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>27022</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>15735</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37424</t>
+          <t>36333</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13706</t>
+          <t>13748</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27461</t>
+          <t>28383</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33218</t>
+          <t>33746</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58012</t>
+          <t>58186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29232</t>
+          <t>28074</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>21257</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20025</t>
+          <t>19863</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42790</t>
+          <t>43456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21395</t>
+          <t>21445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21899</t>
+          <t>21545</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>125970</t>
+          <t>126916</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>368775</t>
+          <t>369910</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28027</t>
+          <t>27299</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46394</t>
+          <t>45961</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158309</t>
+          <t>160563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>450682</t>
+          <t>449981</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,88%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83999</t>
+          <t>81526</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14383</t>
+          <t>14684</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29341</t>
+          <t>28441</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15426</t>
+          <t>17204</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102037</t>
+          <t>100852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12272</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>128348</t>
+          <t>129915</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23626</t>
+          <t>22946</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39313</t>
+          <t>39865</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>25542</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>154496</t>
+          <t>158424</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52225</t>
+          <t>52163</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>10444</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22539</t>
+          <t>22161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>9565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70005</t>
+          <t>69283</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23328</t>
+          <t>23670</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19849</t>
+          <t>19695</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44316</t>
+          <t>42748</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19844</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37396</t>
+          <t>36813</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16249</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30408</t>
+          <t>31289</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40169</t>
+          <t>39887</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62697</t>
+          <t>63032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16737</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10751</t>
+          <t>11080</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24320</t>
+          <t>23748</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>17975</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36193</t>
+          <t>35675</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26754</t>
+          <t>27276</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>11740</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25330</t>
+          <t>24713</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26622</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>46576</t>
+          <t>46738</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>18352</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26570</t>
+          <t>25948</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22819</t>
+          <t>22314</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11184</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25137</t>
+          <t>25462</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20847</t>
+          <t>20616</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41766</t>
+          <t>41186</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>35948</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56447</t>
+          <t>57222</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22833</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38320</t>
+          <t>38851</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63296</t>
+          <t>63374</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91422</t>
+          <t>90555</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,21%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21486</t>
+          <t>21772</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20250</t>
+          <t>20277</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>19318</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37650</t>
+          <t>36569</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18560</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>37247</t>
+          <t>37538</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19203</t>
+          <t>19410</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33813</t>
+          <t>34546</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>42113</t>
+          <t>40977</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>65965</t>
+          <t>64555</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17336</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16866</t>
+          <t>17267</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13154</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30240</t>
+          <t>29718</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>19609</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>14535</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>11466</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28511</t>
+          <t>28407</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>227225</t>
+          <t>229446</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>565312</t>
+          <t>556799</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>102752</t>
+          <t>102048</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>133244</t>
+          <t>132418</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>342019</t>
+          <t>340835</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>748533</t>
+          <t>778705</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>76,1%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21687</t>
+          <t>23368</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>107141</t>
+          <t>108646</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>45612</t>
+          <t>46340</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69276</t>
+          <t>69935</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>63163</t>
+          <t>55714</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>169109</t>
+          <t>166950</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44185</t>
+          <t>48351</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>193213</t>
+          <t>192192</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>79693</t>
+          <t>79729</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>108134</t>
+          <t>108060</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>113713</t>
+          <t>98404</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>283768</t>
+          <t>288552</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16764</t>
+          <t>20102</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>91497</t>
+          <t>88899</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>36545</t>
+          <t>35998</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>58537</t>
+          <t>57825</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>45864</t>
+          <t>44482</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>138429</t>
+          <t>136708</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12884</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>72361</t>
+          <t>72114</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51039</t>
+          <t>50779</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>36087</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>114338</t>
+          <t>112822</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6704-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6704-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45927</t>
+          <t>47364</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75422</t>
+          <t>76362</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>21913</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42988</t>
+          <t>43430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75193</t>
+          <t>77128</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110624</t>
+          <t>111863</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44095</t>
+          <t>45232</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72490</t>
+          <t>71869</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28434</t>
+          <t>28638</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52380</t>
+          <t>50390</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78378</t>
+          <t>77486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112548</t>
+          <t>116023</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66346</t>
+          <t>67204</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95558</t>
+          <t>97665</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39595</t>
+          <t>39393</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64202</t>
+          <t>63364</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112726</t>
+          <t>112099</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>151934</t>
+          <t>152953</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30462</t>
+          <t>28764</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53867</t>
+          <t>53330</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16321</t>
+          <t>16558</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34140</t>
+          <t>34834</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49941</t>
+          <t>50797</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80809</t>
+          <t>81604</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21251</t>
+          <t>21085</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42795</t>
+          <t>41432</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9394</t>
+          <t>8555</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24153</t>
+          <t>24163</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34477</t>
+          <t>34460</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60981</t>
+          <t>60591</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54252</t>
+          <t>53745</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86730</t>
+          <t>85785</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53150</t>
+          <t>53683</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83930</t>
+          <t>84506</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113072</t>
+          <t>116002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157481</t>
+          <t>159308</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60520</t>
+          <t>62019</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94829</t>
+          <t>94076</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31652</t>
+          <t>31470</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55188</t>
+          <t>55764</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100523</t>
+          <t>99476</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140739</t>
+          <t>141893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>108276</t>
+          <t>108118</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146702</t>
+          <t>148193</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59879</t>
+          <t>59785</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90237</t>
+          <t>90445</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>176442</t>
+          <t>175121</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>223920</t>
+          <t>223714</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>47473</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79483</t>
+          <t>78369</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31605</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55452</t>
+          <t>54749</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87499</t>
+          <t>88408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126576</t>
+          <t>126422</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59780</t>
+          <t>60054</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93157</t>
+          <t>93212</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31268</t>
+          <t>31121</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57659</t>
+          <t>56052</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97218</t>
+          <t>99044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>139352</t>
+          <t>139722</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56699</t>
+          <t>57063</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87858</t>
+          <t>88452</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29207</t>
+          <t>28299</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53075</t>
+          <t>52670</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91734</t>
+          <t>90225</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>131265</t>
+          <t>130308</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35846</t>
+          <t>35262</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63531</t>
+          <t>63406</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>28279</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54130</t>
+          <t>52812</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69903</t>
+          <t>69515</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>110141</t>
+          <t>105810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72062</t>
+          <t>73366</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>103733</t>
+          <t>107373</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41125</t>
+          <t>41109</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69001</t>
+          <t>68459</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>123547</t>
+          <t>121618</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>165130</t>
+          <t>163657</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29569</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51905</t>
+          <t>54034</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17405</t>
+          <t>17687</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37556</t>
+          <t>38156</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50799</t>
+          <t>52172</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82324</t>
+          <t>84544</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58664</t>
+          <t>58566</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>89587</t>
+          <t>88777</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38169</t>
+          <t>39437</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66568</t>
+          <t>65820</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104488</t>
+          <t>105505</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145989</t>
+          <t>147337</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50479</t>
+          <t>49061</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>81299</t>
+          <t>79624</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67492</t>
+          <t>67571</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99990</t>
+          <t>98857</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>126007</t>
+          <t>124043</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>167387</t>
+          <t>167994</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59490</t>
+          <t>61765</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>94494</t>
+          <t>93815</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31911</t>
+          <t>31509</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>55952</t>
+          <t>56830</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>99640</t>
+          <t>99373</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>139398</t>
+          <t>139840</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>127539</t>
+          <t>127726</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>166890</t>
+          <t>166810</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>78875</t>
+          <t>76967</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>110326</t>
+          <t>109987</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>215372</t>
+          <t>216881</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>267256</t>
+          <t>265501</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,04%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68514</t>
+          <t>67822</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>103994</t>
+          <t>102573</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46091</t>
+          <t>44834</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74984</t>
+          <t>74456</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>124005</t>
+          <t>124885</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>168426</t>
+          <t>167105</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32999</t>
+          <t>32562</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>60232</t>
+          <t>58802</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33654</t>
+          <t>34103</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>53617</t>
+          <t>50790</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>84959</t>
+          <t>83736</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>236036</t>
+          <t>232434</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>293962</t>
+          <t>294235</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>196643</t>
+          <t>197827</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>249781</t>
+          <t>250276</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>445592</t>
+          <t>446656</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>526806</t>
+          <t>528609</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>230590</t>
+          <t>228101</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>289447</t>
+          <t>289612</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>140304</t>
+          <t>140118</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>189136</t>
+          <t>187511</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>384908</t>
+          <t>382883</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>462701</t>
+          <t>462727</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>405344</t>
+          <t>407092</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>478961</t>
+          <t>480633</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>245619</t>
+          <t>245954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>303592</t>
+          <t>301798</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>666891</t>
+          <t>670043</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>763008</t>
+          <t>758840</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>201926</t>
+          <t>200020</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>259664</t>
+          <t>256298</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>128809</t>
+          <t>130429</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>175371</t>
+          <t>175753</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>343976</t>
+          <t>343344</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>415858</t>
+          <t>417368</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>194708</t>
+          <t>194103</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>253580</t>
+          <t>253727</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>111563</t>
+          <t>110890</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>154979</t>
+          <t>156724</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>318245</t>
+          <t>323010</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>395965</t>
+          <t>397127</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34229</t>
+          <t>33713</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58716</t>
+          <t>58192</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33359</t>
+          <t>33402</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55743</t>
+          <t>54764</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72699</t>
+          <t>73917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106111</t>
+          <t>105929</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29165</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53900</t>
+          <t>54622</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27733</t>
+          <t>27584</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49318</t>
+          <t>47971</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63469</t>
+          <t>62206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95408</t>
+          <t>93956</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58071</t>
+          <t>58667</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87252</t>
+          <t>88338</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31283</t>
+          <t>30922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53727</t>
+          <t>52261</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>95577</t>
+          <t>94178</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>131483</t>
+          <t>132188</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46817</t>
+          <t>47715</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74612</t>
+          <t>74457</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21886</t>
+          <t>21800</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43241</t>
+          <t>43258</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75632</t>
+          <t>76046</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110711</t>
+          <t>110850</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17443</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37526</t>
+          <t>37457</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>7607</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>22481</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28027</t>
+          <t>28690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52524</t>
+          <t>53372</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86975</t>
+          <t>88470</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124127</t>
+          <t>124046</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62840</t>
+          <t>62910</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92300</t>
+          <t>93001</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159804</t>
+          <t>158874</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204479</t>
+          <t>206765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51298</t>
+          <t>50719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81044</t>
+          <t>80910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38569</t>
+          <t>37415</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64168</t>
+          <t>63391</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>96961</t>
+          <t>96844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137442</t>
+          <t>138222</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92963</t>
+          <t>96086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>131701</t>
+          <t>133321</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58779</t>
+          <t>58540</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87191</t>
+          <t>88247</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>162820</t>
+          <t>164339</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>210313</t>
+          <t>210209</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67528</t>
+          <t>68304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101956</t>
+          <t>103166</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41173</t>
+          <t>39267</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67895</t>
+          <t>65304</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114537</t>
+          <t>116259</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>156341</t>
+          <t>159383</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34291</t>
+          <t>33471</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60724</t>
+          <t>61285</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13853</t>
+          <t>13521</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31928</t>
+          <t>32523</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53716</t>
+          <t>53015</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>84324</t>
+          <t>86549</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62433</t>
+          <t>60887</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94925</t>
+          <t>94095</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32625</t>
+          <t>32689</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55695</t>
+          <t>56183</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98397</t>
+          <t>101217</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140223</t>
+          <t>141526</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44766</t>
+          <t>45775</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73118</t>
+          <t>74690</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51026</t>
+          <t>49340</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78267</t>
+          <t>77203</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>103278</t>
+          <t>103591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>143917</t>
+          <t>145397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>112921</t>
+          <t>114808</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>151764</t>
+          <t>153624</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>77547</t>
+          <t>79991</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>109137</t>
+          <t>109902</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>203691</t>
+          <t>201782</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>252297</t>
+          <t>251410</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37300</t>
+          <t>37604</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63702</t>
+          <t>63687</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33770</t>
+          <t>34356</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59816</t>
+          <t>58485</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77222</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>114126</t>
+          <t>115293</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34152</t>
+          <t>33716</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59688</t>
+          <t>59880</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17249</t>
+          <t>17129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35805</t>
+          <t>36824</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55836</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88203</t>
+          <t>89418</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87171</t>
+          <t>84519</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122060</t>
+          <t>120535</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>81235</t>
+          <t>81152</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>115100</t>
+          <t>115583</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>176290</t>
+          <t>177517</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>223912</t>
+          <t>225828</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64638</t>
+          <t>64451</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>95480</t>
+          <t>97625</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32412</t>
+          <t>33056</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>57437</t>
+          <t>57764</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>104914</t>
+          <t>106575</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>146982</t>
+          <t>145030</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>91817</t>
+          <t>90899</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>127717</t>
+          <t>128706</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>78584</t>
+          <t>77130</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>110701</t>
+          <t>109817</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>180226</t>
+          <t>177500</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>227844</t>
+          <t>225983</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52580</t>
+          <t>52680</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>81207</t>
+          <t>81045</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39616</t>
+          <t>40372</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67048</t>
+          <t>68016</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>97823</t>
+          <t>98081</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>139246</t>
+          <t>137355</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31889</t>
+          <t>31825</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58760</t>
+          <t>57864</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>27721</t>
+          <t>27398</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50997</t>
+          <t>50040</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>65834</t>
+          <t>65028</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>99489</t>
+          <t>99638</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>297852</t>
+          <t>296085</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>364025</t>
+          <t>361946</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>234818</t>
+          <t>232440</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>289169</t>
+          <t>291352</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>545117</t>
+          <t>544864</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>633923</t>
+          <t>636076</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>213395</t>
+          <t>211755</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>272993</t>
+          <t>273307</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>169954</t>
+          <t>168720</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>221574</t>
+          <t>220166</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>401456</t>
+          <t>402451</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>481446</t>
+          <t>477603</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>391655</t>
+          <t>392772</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>461577</t>
+          <t>463506</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>272475</t>
+          <t>270491</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>328926</t>
+          <t>330828</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>683088</t>
+          <t>681546</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>778465</t>
+          <t>776661</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>230783</t>
+          <t>232805</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>290176</t>
+          <t>293943</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>157072</t>
+          <t>155286</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>205160</t>
+          <t>205961</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>403486</t>
+          <t>401108</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>479824</t>
+          <t>479198</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>138043</t>
+          <t>135475</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>185178</t>
+          <t>186432</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>82201</t>
+          <t>79381</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>118316</t>
+          <t>119626</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>230405</t>
+          <t>230553</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>294417</t>
+          <t>291617</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -8011,32 +8011,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25525</t>
+          <t>27443</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15771</t>
+          <t>18050</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40134</t>
+          <t>39154</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8046,32 +8046,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27523</t>
+          <t>31296</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20954</t>
+          <t>23318</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35164</t>
+          <t>39143</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8081,32 +8081,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>53048</t>
+          <t>58738</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41234</t>
+          <t>44585</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69846</t>
+          <t>73166</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>41,58%</t>
         </is>
       </c>
     </row>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21568</t>
+          <t>23393</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8159,32 +8159,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11172</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8194,32 +8194,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>18438</t>
+          <t>20417</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11854</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27022</t>
+          <t>30609</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -8237,32 +8237,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25360</t>
+          <t>28075</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15735</t>
+          <t>18836</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36333</t>
+          <t>40048</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8272,32 +8272,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19606</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>15977</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28383</t>
+          <t>31869</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8307,32 +8307,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>44966</t>
+          <t>50835</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33746</t>
+          <t>38890</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58186</t>
+          <t>65546</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,25%</t>
         </is>
       </c>
     </row>
@@ -8350,32 +8350,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15744</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28074</t>
+          <t>33627</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8385,32 +8385,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14402</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9975</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21257</t>
+          <t>23264</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8420,32 +8420,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30146</t>
+          <t>33309</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19863</t>
+          <t>22805</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43456</t>
+          <t>49025</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -8463,32 +8463,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>10694</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21445</t>
+          <t>24006</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8498,32 +8498,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>472</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8533,32 +8533,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10863</t>
+          <t>12649</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21545</t>
+          <t>26660</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -8576,17 +8576,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8611,17 +8611,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8646,17 +8646,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8693,32 +8693,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>296844</t>
+          <t>58617</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126916</t>
+          <t>44462</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>369910</t>
+          <t>71476</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8728,32 +8728,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36159</t>
+          <t>39811</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27299</t>
+          <t>30449</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45961</t>
+          <t>48739</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8763,32 +8763,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>333003</t>
+          <t>98428</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160563</t>
+          <t>81461</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>449981</t>
+          <t>116818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -8806,32 +8806,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28916</t>
+          <t>29397</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>19923</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81526</t>
+          <t>40509</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8841,32 +8841,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20608</t>
+          <t>23482</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28441</t>
+          <t>31518</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8876,32 +8876,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>49524</t>
+          <t>52879</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17204</t>
+          <t>40718</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100852</t>
+          <t>67004</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -8919,32 +8919,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>45754</t>
+          <t>52810</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11041</t>
+          <t>40490</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>129915</t>
+          <t>68378</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8954,32 +8954,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30763</t>
+          <t>33166</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22946</t>
+          <t>25340</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39865</t>
+          <t>42242</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8989,32 +8989,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>76517</t>
+          <t>85976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25542</t>
+          <t>71533</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>158424</t>
+          <t>100937</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -9032,32 +9032,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17476</t>
+          <t>21421</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>13024</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52163</t>
+          <t>33005</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9067,32 +9067,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15173</t>
+          <t>17047</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10444</t>
+          <t>11549</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22161</t>
+          <t>26160</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9102,32 +9102,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>32649</t>
+          <t>38468</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>28448</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69283</t>
+          <t>51333</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -9145,32 +9145,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>14555</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9180,32 +9180,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19695</t>
+          <t>22219</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9215,32 +9215,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>21620</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>14041</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42748</t>
+          <t>31972</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -9258,17 +9258,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>396408</t>
+          <t>170030</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>396408</t>
+          <t>170030</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>396408</t>
+          <t>170030</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9293,17 +9293,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>115628</t>
+          <t>127342</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>115628</t>
+          <t>127342</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>115628</t>
+          <t>127342</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9328,17 +9328,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>512036</t>
+          <t>297372</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>512036</t>
+          <t>297372</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>512036</t>
+          <t>297372</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9375,32 +9375,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>27761</t>
+          <t>34672</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18571</t>
+          <t>24739</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36813</t>
+          <t>48873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9410,32 +9410,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>25106</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15951</t>
+          <t>17782</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31289</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9445,32 +9445,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>50894</t>
+          <t>59779</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39887</t>
+          <t>46231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63032</t>
+          <t>74981</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -9488,22 +9488,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>10700</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16126</t>
+          <t>19063</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9523,32 +9523,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16833</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11080</t>
+          <t>13038</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23748</t>
+          <t>26826</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9558,32 +9558,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>25899</t>
+          <t>29708</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17975</t>
+          <t>19796</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35675</t>
+          <t>41007</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -9601,32 +9601,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17805</t>
+          <t>20288</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>12174</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27276</t>
+          <t>30644</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9636,32 +9636,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17648</t>
+          <t>20200</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11740</t>
+          <t>14040</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24713</t>
+          <t>27776</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9671,32 +9671,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>35454</t>
+          <t>40487</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>29392</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>46738</t>
+          <t>53695</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -9714,32 +9714,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>13808</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>24369</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9749,32 +9749,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>14256</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9784,32 +9784,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>21896</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9367</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25948</t>
+          <t>33263</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -9827,32 +9827,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>13655</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22314</t>
+          <t>23732</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9862,32 +9862,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17051</t>
+          <t>19129</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>12583</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25462</t>
+          <t>27661</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9897,32 +9897,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>30051</t>
+          <t>32785</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20616</t>
+          <t>22652</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41186</t>
+          <t>47378</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -9940,17 +9940,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9975,17 +9975,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10010,17 +10010,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>51867</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35948</t>
+          <t>39919</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57222</t>
+          <t>63535</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>30447</t>
+          <t>34302</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23312</t>
+          <t>26161</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38851</t>
+          <t>42340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>76457</t>
+          <t>86169</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63374</t>
+          <t>71987</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90555</t>
+          <t>99933</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -10170,27 +10170,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>14834</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>23614</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -10205,32 +10205,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13871</t>
+          <t>15320</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8873</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20277</t>
+          <t>22918</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10240,32 +10240,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>27130</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19318</t>
+          <t>22127</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36569</t>
+          <t>40334</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -10283,32 +10283,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27173</t>
+          <t>26834</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>17443</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>37538</t>
+          <t>36354</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10318,32 +10318,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>25902</t>
+          <t>28127</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19410</t>
+          <t>20470</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34546</t>
+          <t>36343</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10353,32 +10353,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>53075</t>
+          <t>54961</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>40977</t>
+          <t>43964</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>64555</t>
+          <t>68050</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>31,83%</t>
         </is>
       </c>
     </row>
@@ -10396,32 +10396,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17874</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10431,32 +10431,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>11079</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17267</t>
+          <t>17484</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10466,32 +10466,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>20691</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>14196</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29718</t>
+          <t>30915</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -10509,32 +10509,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11224</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19609</t>
+          <t>22296</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10544,32 +10544,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14535</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10579,32 +10579,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>18596</t>
+          <t>21276</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11466</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28407</t>
+          <t>32078</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10657,17 +10657,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>88300</t>
+          <t>96986</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>88300</t>
+          <t>96986</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>88300</t>
+          <t>96986</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10692,17 +10692,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>195950</t>
+          <t>213763</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>195950</t>
+          <t>213763</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>195950</t>
+          <t>213763</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>396140</t>
+          <t>172599</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>229446</t>
+          <t>147491</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>556799</t>
+          <t>197220</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>117261</t>
+          <t>130515</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>102048</t>
+          <t>113720</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>132418</t>
+          <t>148555</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>513401</t>
+          <t>303114</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>340835</t>
+          <t>274686</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>778705</t>
+          <t>339614</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -10852,32 +10852,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>63968</t>
+          <t>69194</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23368</t>
+          <t>54639</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>108646</t>
+          <t>86069</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10887,32 +10887,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>57023</t>
+          <t>63964</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>46340</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69935</t>
+          <t>77476</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10922,32 +10922,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>120991</t>
+          <t>133157</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>55714</t>
+          <t>112739</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>166950</t>
+          <t>155600</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -10965,32 +10965,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>116092</t>
+          <t>128007</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48351</t>
+          <t>106400</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>192192</t>
+          <t>149723</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11000,32 +11000,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>93919</t>
+          <t>104252</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>79729</t>
+          <t>90381</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>108060</t>
+          <t>122875</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11035,32 +11035,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>210012</t>
+          <t>232259</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>98404</t>
+          <t>205846</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>288552</t>
+          <t>262775</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -11078,32 +11078,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>63044</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20102</t>
+          <t>46851</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>88899</t>
+          <t>85117</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11113,32 +11113,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>46442</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>35998</t>
+          <t>41348</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>57825</t>
+          <t>66910</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11148,32 +11148,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>99027</t>
+          <t>114876</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>44482</t>
+          <t>95337</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>136708</t>
+          <t>138418</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -11191,32 +11191,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>41175</t>
+          <t>45251</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>15054</t>
+          <t>32335</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>72114</t>
+          <t>64032</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11226,32 +11226,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>38680</t>
+          <t>43079</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28646</t>
+          <t>32252</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>50779</t>
+          <t>55962</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11261,32 +11261,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>79855</t>
+          <t>88330</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>36087</t>
+          <t>70546</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>112822</t>
+          <t>109406</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -11304,17 +11304,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478095</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478095</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478095</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11339,17 +11339,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>353325</t>
+          <t>393642</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>353325</t>
+          <t>393642</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>353325</t>
+          <t>393642</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11374,17 +11374,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1023286</t>
+          <t>871737</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1023286</t>
+          <t>871737</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1023286</t>
+          <t>871737</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
